--- a/reports/pdf_change_20260909.xlsx
+++ b/reports/pdf_change_20260909.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억   ·   현금 21억(0.5%)      당일 2026-09-09  vs  전영업일 2026-09-08      매수 5종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억      당일 2026-09-09  vs  전영업일 2026-09-08      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -728,23 +728,23 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-4323900000</v>
+        <v>-4217325000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2.21%→1.16%</t>
+          <t>4.96%→3.96%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>33→18</t>
+          <t>78→63</t>
         </is>
       </c>
     </row>
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-4217325000</v>
+        <v>-4323900000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>4.96%→3.96%</t>
+          <t>2.21%→1.16%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>78→63</t>
+          <t>33→18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,518억   ·   현금 44억(1.2%)      당일 2026-09-09  vs  전영업일 2026-09-08      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,518억      당일 2026-09-09  vs  전영업일 2026-09-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -891,7 +891,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 34억(1.4%)      당일 2026-09-09  vs  전영업일 2026-09-08      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억      당일 2026-09-09  vs  전영업일 2026-09-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -915,7 +915,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,991억   ·   현금 4억(0.2%)      당일 2026-09-09  vs  전영업일 2026-09-08      매수 1종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,991억      당일 2026-09-09  vs  전영업일 2026-09-08      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1032,7 +1032,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 270억   ·   현금 1억(0.5%)      당일 2026-09-09  vs  전영업일 2026-09-08      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 270억      당일 2026-09-09  vs  전영업일 2026-09-08      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1253,7 +1253,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 498억   ·   현금 4억(0.8%)      당일 2026-09-09  vs  전영업일 2026-09-08      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 498억      당일 2026-09-09  vs  전영업일 2026-09-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
